--- a/docs/result/row-data/1st-test/pessimistic/pessimistic-lock-1000-ngrinder-result.xlsx
+++ b/docs/result/row-data/1st-test/pessimistic/pessimistic-lock-1000-ngrinder-result.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sangja/Projects/concurrency-control-benchmarks/docs/result/row-data/1st-test/pessimistic/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F92E0775-421A-BE47-8BAF-1B306FC79782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A642CEF9-B9F4-BA42-8CB7-BFDE00C28DDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="14700" windowHeight="18460" xr2:uid="{12F202AF-9566-A44C-95DC-B832A6C0E1EC}"/>
+    <workbookView xWindow="14700" yWindow="660" windowWidth="14700" windowHeight="18460" xr2:uid="{12F202AF-9566-A44C-95DC-B832A6C0E1EC}"/>
   </bookViews>
   <sheets>
     <sheet name="pessimistic-lock-1000-ngrinder-" sheetId="1" r:id="rId1"/>
@@ -742,8 +742,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="268407" cy="345992"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="TextBox 1">
@@ -828,7 +828,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="TextBox 1">
@@ -896,8 +896,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="279628" cy="345992"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="TextBox 2">
@@ -982,7 +982,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="TextBox 2">
@@ -1050,8 +1050,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="185692" cy="345992"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="4" name="TextBox 3">
@@ -1136,7 +1136,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="4" name="TextBox 3">
@@ -1204,8 +1204,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="453907" cy="345992"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="5" name="TextBox 4">
@@ -1321,7 +1321,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="5" name="TextBox 4">
@@ -1389,8 +1389,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1049454" cy="359009"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="6" name="TextBox 5">
@@ -1559,7 +1559,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="6" name="TextBox 5">
@@ -1627,8 +1627,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="806503" cy="359009"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="7" name="TextBox 6">
@@ -1766,7 +1766,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="7" name="TextBox 6">
@@ -1834,8 +1834,8 @@
       <xdr:rowOff>226785</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1303947" cy="498929"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="8" name="TextBox 7">
@@ -2126,7 +2126,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="8" name="TextBox 7">
@@ -2194,8 +2194,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="241300" cy="527004"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="9" name="TextBox 8">
@@ -2291,7 +2291,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="9" name="TextBox 8">
@@ -2362,8 +2362,8 @@
       <xdr:rowOff>226785</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="253787" cy="527324"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="10" name="TextBox 9">
@@ -2459,7 +2459,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="10" name="TextBox 9">
@@ -2530,8 +2530,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1056379" cy="281214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="11" name="TextBox 10">
@@ -2739,7 +2739,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="11" name="TextBox 10">
@@ -2825,8 +2825,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="726930" cy="264885"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="12" name="TextBox 11">
@@ -2972,7 +2972,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="12" name="TextBox 11">
@@ -3043,8 +3043,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1014380" cy="244929"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="29" name="TextBox 28">
@@ -3240,7 +3240,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="29" name="TextBox 28">
@@ -3308,8 +3308,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1759858" cy="498929"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="30" name="TextBox 29">
@@ -3665,7 +3665,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="30" name="TextBox 29">
@@ -3733,8 +3733,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2239972" cy="248557"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="31" name="TextBox 30">
@@ -3957,7 +3957,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="31" name="TextBox 30">
@@ -4025,8 +4025,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1559722" cy="553357"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="32" name="TextBox 31">
@@ -4241,7 +4241,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="32" name="TextBox 31">
@@ -4309,8 +4309,8 @@
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1559722" cy="453572"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="33" name="TextBox 32">
@@ -4502,7 +4502,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="33" name="TextBox 32">
@@ -4570,8 +4570,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2071786" cy="182999"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="34" name="TextBox 33">
@@ -4726,7 +4726,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="34" name="TextBox 33">
@@ -4782,6 +4782,1464 @@
                 <a:t>"</a:t>
               </a:r>
               <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="738151" cy="355097"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="13" name="TextBox 12">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{698964A4-12A0-3647-8CC8-27E9261EA8D1}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4203700" y="4800600"/>
+              <a:ext cx="738151" cy="355097"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:d>
+                      <m:dPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:dPr>
+                      <m:e>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑛</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑖</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>−1</m:t>
+                        </m:r>
+                      </m:e>
+                    </m:d>
+                    <m:sSubSup>
+                      <m:sSubSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubSupPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝜎</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                      </m:sub>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>2</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSubSup>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+            <a:p>
+              <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="13" name="TextBox 12">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{698964A4-12A0-3647-8CC8-27E9261EA8D1}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4203700" y="4800600"/>
+              <a:ext cx="738151" cy="355097"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>(𝑛_𝑖−1) </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝜎_</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑖^2</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+            <a:p>
+              <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1599284" cy="182871"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="14" name="TextBox 13">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{999B05E2-35AC-9644-908D-1E2228341142}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4203700" y="6629400"/>
+              <a:ext cx="1599284" cy="182871"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑆</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑆</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑤𝑖𝑡h𝑖𝑛</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                    <m:sSubSup>
+                      <m:sSubSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubSupPr>
+                      <m:e>
+                        <m:r>
+                          <m:rPr>
+                            <m:sty m:val="p"/>
+                          </m:rPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>Σ</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>=1</m:t>
+                        </m:r>
+                      </m:sub>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>2</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSubSup>
+                    <m:d>
+                      <m:dPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:dPr>
+                      <m:e>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑛</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑖</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>−1</m:t>
+                        </m:r>
+                      </m:e>
+                    </m:d>
+                    <m:sSubSup>
+                      <m:sSubSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubSupPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝜎</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                      </m:sub>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>2</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSubSup>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="14" name="TextBox 13">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{999B05E2-35AC-9644-908D-1E2228341142}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4203700" y="6629400"/>
+              <a:ext cx="1599284" cy="182871"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑆𝑆_𝑤𝑖𝑡ℎ𝑖𝑛=Σ_(𝑖=1)^2 (𝑛_𝑖−1) 𝜎_𝑖^2</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="964816" cy="177228"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="15" name="TextBox 14">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8ABA77CE-3CD9-214A-99A4-86FF87219E8B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4203700" y="7086600"/>
+              <a:ext cx="964816" cy="177228"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑛</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:sSup>
+                      <m:sSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSupPr>
+                      <m:e>
+                        <m:d>
+                          <m:dPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:dPr>
+                          <m:e>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝜇</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑖</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>−</m:t>
+                            </m:r>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝜇</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡𝑜𝑡𝑎𝑙</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                          </m:e>
+                        </m:d>
+                      </m:e>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>2</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSup>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="15" name="TextBox 14">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8ABA77CE-3CD9-214A-99A4-86FF87219E8B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4203700" y="7086600"/>
+              <a:ext cx="964816" cy="177228"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑛_𝑖 (𝜇_𝑖−𝜇_𝑡𝑜𝑡𝑎𝑙 )^2</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1984902" cy="186782"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="16" name="TextBox 15">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{785EE641-D580-3349-A9A9-15E99312D904}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4203700" y="8915400"/>
+              <a:ext cx="1984902" cy="186782"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑆</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑆</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑏𝑒𝑡𝑤𝑒𝑒𝑛</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                    <m:sSubSup>
+                      <m:sSubSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubSupPr>
+                      <m:e>
+                        <m:r>
+                          <m:rPr>
+                            <m:sty m:val="p"/>
+                          </m:rPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>Σ</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>=1</m:t>
+                        </m:r>
+                      </m:sub>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑘</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSubSup>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑛</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:sSup>
+                      <m:sSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSupPr>
+                      <m:e>
+                        <m:d>
+                          <m:dPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:dPr>
+                          <m:e>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝜇</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑖</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>−</m:t>
+                            </m:r>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝜇</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡𝑜𝑡𝑎𝑙</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                          </m:e>
+                        </m:d>
+                      </m:e>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>2</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSup>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="16" name="TextBox 15">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{785EE641-D580-3349-A9A9-15E99312D904}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4203700" y="8915400"/>
+              <a:ext cx="1984902" cy="186782"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑆𝑆_𝑏𝑒𝑡𝑤𝑒𝑒𝑛=Σ_(𝑖=1)^𝑘 𝑛_𝑖 (𝜇_𝑖−𝜇_𝑡𝑜𝑡𝑎𝑙 )^2</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1842235" cy="500137"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="17" name="TextBox 16">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D16D8197-9955-ED42-949A-B7E344AFD5C7}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4203700" y="9372600"/>
+              <a:ext cx="1842235" cy="500137"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝜎</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <m:rPr>
+                            <m:sty m:val="p"/>
+                          </m:rPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>total</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                    <m:rad>
+                      <m:radPr>
+                        <m:degHide m:val="on"/>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:radPr>
+                      <m:deg/>
+                      <m:e>
+                        <m:f>
+                          <m:fPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:fPr>
+                          <m:num>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <m:rPr>
+                                    <m:sty m:val="p"/>
+                                  </m:rPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>SS</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <m:rPr>
+                                    <m:sty m:val="p"/>
+                                  </m:rPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>within</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>+</m:t>
+                            </m:r>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <m:rPr>
+                                    <m:sty m:val="p"/>
+                                  </m:rPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>SS</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <m:rPr>
+                                    <m:sty m:val="p"/>
+                                  </m:rPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>between</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                          </m:num>
+                          <m:den>
+                            <m:r>
+                              <m:rPr>
+                                <m:sty m:val="p"/>
+                              </m:rPr>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>N</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>-1</m:t>
+                            </m:r>
+                          </m:den>
+                        </m:f>
+                      </m:e>
+                    </m:rad>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="17" name="TextBox 16">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D16D8197-9955-ED42-949A-B7E344AFD5C7}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4203700" y="9372600"/>
+              <a:ext cx="1842235" cy="500137"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝜎_</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>total=√((SS_within+SS_between)/(N-1))</a:t>
+              </a:r>
+              <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="438710" cy="173766"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="18" name="TextBox 17">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A775239-3DBB-7D4A-8A86-BE60A771483A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4203700" y="10058400"/>
+              <a:ext cx="438710" cy="173766"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>2</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝜎</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑡𝑜𝑡𝑎𝑙</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="18" name="TextBox 17">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A775239-3DBB-7D4A-8A86-BE60A771483A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4203700" y="10058400"/>
+              <a:ext cx="438710" cy="173766"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>2𝜎_𝑡𝑜𝑡𝑎𝑙</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -5115,7 +6573,7 @@
     <col min="1" max="1" width="25.85546875" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
     <col min="5" max="5" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="30.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.7109375" bestFit="1" customWidth="1"/>
@@ -5498,377 +6956,469 @@
     </row>
     <row r="14" spans="1:13">
       <c r="A14">
-        <f>C2</f>
+        <f t="shared" ref="A14:A21" si="0">C2</f>
         <v>172</v>
       </c>
       <c r="B14">
-        <f>E2</f>
+        <f t="shared" ref="B14:C21" si="1">E2</f>
         <v>506.91300000000001</v>
       </c>
       <c r="C14">
-        <f>F2</f>
+        <f t="shared" si="1"/>
         <v>532.16499999999996</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15">
-        <f>C3</f>
+        <f t="shared" si="0"/>
         <v>414</v>
       </c>
       <c r="B15">
-        <f>E3</f>
+        <f t="shared" si="1"/>
         <v>1133.174</v>
       </c>
       <c r="C15">
-        <f>F3</f>
+        <f t="shared" si="1"/>
         <v>485.238</v>
       </c>
     </row>
     <row r="16" spans="1:13">
       <c r="A16">
-        <f>C4</f>
+        <f t="shared" si="0"/>
         <v>211</v>
       </c>
       <c r="B16">
-        <f>E4</f>
+        <f t="shared" si="1"/>
         <v>1491.5170000000001</v>
       </c>
       <c r="C16">
-        <f>F4</f>
+        <f t="shared" si="1"/>
         <v>580.577</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:5">
       <c r="A17">
-        <f>C5</f>
+        <f t="shared" si="0"/>
         <v>193</v>
       </c>
       <c r="B17">
-        <f>E5</f>
+        <f t="shared" si="1"/>
         <v>1004.85</v>
       </c>
       <c r="C17">
-        <f>F5</f>
+        <f t="shared" si="1"/>
         <v>481.79700000000003</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:5">
       <c r="A18">
-        <f>C6</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B18">
-        <f>E6</f>
+        <f t="shared" si="1"/>
         <v>11.222</v>
       </c>
       <c r="C18">
-        <f>F6</f>
+        <f t="shared" si="1"/>
         <v>4.4909999999999997</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:5">
       <c r="A19">
-        <f>C7</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="B19">
-        <f>E7</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C19">
-        <f>F7</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:5">
       <c r="A20">
-        <f>C8</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="B20">
-        <f>E8</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C20">
-        <f>F8</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:5">
       <c r="A21">
-        <f>C9</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="B21">
-        <f>E9</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="C21">
-        <f>F9</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="22" spans="1:5">
+      <c r="E22">
+        <f>(A14-1)*POWER(C14,2)</f>
+        <v>48427129.415474996</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="B23">
-        <f>A14*B14</f>
+        <f t="shared" ref="B23:B30" si="2">A14*B14</f>
         <v>87189.036000000007</v>
       </c>
+      <c r="E23">
+        <f>(A15-1)*POWER(C15,2)</f>
+        <v>97243293.573972002</v>
+      </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:5">
       <c r="B24">
-        <f>A15*B15</f>
+        <f t="shared" si="2"/>
         <v>469134.03599999996</v>
       </c>
+      <c r="E24">
+        <f>(A16-1)*POWER(C16,2)</f>
+        <v>70784627.115089998</v>
+      </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:5">
       <c r="B25">
-        <f>A16*B16</f>
+        <f t="shared" si="2"/>
         <v>314710.087</v>
       </c>
+      <c r="E25">
+        <f>(A17-1)*POWER(C17,2)</f>
+        <v>44568643.048128009</v>
+      </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:5">
       <c r="B26">
-        <f>A17*B17</f>
+        <f t="shared" si="2"/>
         <v>193936.05000000002</v>
       </c>
+      <c r="E26">
+        <f>(A18-1)*POWER(C18,2)</f>
+        <v>161.35264799999999</v>
+      </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:5">
       <c r="B27">
-        <f>A18*B18</f>
+        <f t="shared" si="2"/>
         <v>100.99799999999999</v>
       </c>
+      <c r="E27">
+        <f>(A19-1)*POWER(C19,2)</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:5">
       <c r="B28">
-        <f>A19*B19</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
+      <c r="E28">
+        <f>(A20-1)*POWER(C20,2)</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:5">
       <c r="B29">
-        <f>A20*B20</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
+      <c r="E29">
+        <f>(A21-1)*POWER(C21,2)</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:5">
       <c r="B30">
-        <f>A21*B21</f>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
+      <c r="E30">
+        <f>SUM(E22:E29)</f>
+        <v>261023854.50531301</v>
+      </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:5">
       <c r="B31">
         <f>SUM(B23:B30)</f>
         <v>1065082.2069999999</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:5">
       <c r="B32">
         <f>SUM(A14:A21)</f>
         <v>1000</v>
       </c>
+      <c r="E32">
+        <f>A14*POWER(B14-B$33,2)</f>
+        <v>53587092.546597503</v>
+      </c>
     </row>
-    <row r="33" spans="2:2">
+    <row r="33" spans="2:5">
       <c r="B33">
         <f>B31/B32</f>
         <v>1065.0822069999999</v>
       </c>
+      <c r="E33">
+        <f>A15*POWER(B15-B$33,2)</f>
+        <v>1919507.8014173105</v>
+      </c>
     </row>
-    <row r="34" spans="2:2">
+    <row r="34" spans="2:5">
       <c r="B34">
         <f>ROUND(B33,2)</f>
         <v>1065.08</v>
       </c>
+      <c r="E34">
+        <f>A16*POWER(B16-B$33,2)</f>
+        <v>38369639.495681077</v>
+      </c>
     </row>
-    <row r="36" spans="2:2">
+    <row r="35" spans="2:5">
+      <c r="E35">
+        <f>A17*POWER(B17-B$33,2)</f>
+        <v>700188.32069753157</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5">
       <c r="B36">
-        <f>POWER(C14,2)</f>
+        <f t="shared" ref="B36:B43" si="3">POWER(C14,2)</f>
         <v>283199.58722499997</v>
       </c>
+      <c r="E36">
+        <f>A18*POWER(B18-B$33,2)</f>
+        <v>9995592.0230827443</v>
+      </c>
     </row>
-    <row r="37" spans="2:2">
+    <row r="37" spans="2:5">
       <c r="B37">
-        <f>POWER(C15,2)</f>
+        <f t="shared" si="3"/>
         <v>235455.91664400001</v>
       </c>
+      <c r="E37">
+        <f>A19*POWER(B19-B$33,2)</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="38" spans="2:2">
+    <row r="38" spans="2:5">
       <c r="B38">
-        <f>POWER(C16,2)</f>
+        <f t="shared" si="3"/>
         <v>337069.65292899997</v>
       </c>
+      <c r="E38">
+        <f>A20*POWER(B20-B$33,2)</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="39" spans="2:2">
+    <row r="39" spans="2:5">
       <c r="B39">
-        <f>POWER(C17,2)</f>
+        <f t="shared" si="3"/>
         <v>232128.34920900004</v>
       </c>
+      <c r="E39">
+        <f>A21*POWER(B21-B$33,2)</f>
+        <v>1108982.1346999907</v>
+      </c>
     </row>
-    <row r="40" spans="2:2">
+    <row r="40" spans="2:5">
       <c r="B40">
-        <f>POWER(C18,2)</f>
+        <f t="shared" si="3"/>
         <v>20.169080999999998</v>
       </c>
+      <c r="E40">
+        <f>SUM(E32:E39)</f>
+        <v>105681002.32217616</v>
+      </c>
     </row>
-    <row r="41" spans="2:2">
+    <row r="41" spans="2:5">
       <c r="B41">
-        <f>POWER(C19,2)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="2:2">
+    <row r="42" spans="2:5">
       <c r="B42">
-        <f>POWER(C20,2)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
+      <c r="E42">
+        <f>SQRT((E30+E40)/(B32-1))</f>
+        <v>605.86461256310838</v>
+      </c>
     </row>
-    <row r="43" spans="2:2">
+    <row r="43" spans="2:5">
       <c r="B43">
-        <f>POWER(C21,2)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
+      <c r="E43">
+        <f>ROUND(E42,2)</f>
+        <v>605.86</v>
+      </c>
     </row>
-    <row r="44" spans="2:2">
+    <row r="44" spans="2:5">
       <c r="B44">
-        <f>POWER(B14,2)</f>
+        <f t="shared" ref="B44:B51" si="4">POWER(B14,2)</f>
         <v>256960.78956900002</v>
       </c>
     </row>
-    <row r="45" spans="2:2">
+    <row r="45" spans="2:5">
       <c r="B45">
-        <f>POWER(B15,2)</f>
+        <f t="shared" si="4"/>
         <v>1284083.314276</v>
       </c>
+      <c r="E45">
+        <f>2*E42</f>
+        <v>1211.7292251262168</v>
+      </c>
     </row>
-    <row r="46" spans="2:2">
+    <row r="46" spans="2:5">
       <c r="B46">
-        <f>POWER(B16,2)</f>
+        <f t="shared" si="4"/>
         <v>2224622.9612890002</v>
       </c>
+      <c r="E46">
+        <f>ROUND(E45,2)</f>
+        <v>1211.73</v>
+      </c>
     </row>
-    <row r="47" spans="2:2">
+    <row r="47" spans="2:5">
       <c r="B47">
-        <f>POWER(B17,2)</f>
+        <f t="shared" si="4"/>
         <v>1009723.5225000001</v>
       </c>
     </row>
-    <row r="48" spans="2:2">
+    <row r="48" spans="2:5">
       <c r="B48">
-        <f>POWER(B18,2)</f>
+        <f t="shared" si="4"/>
         <v>125.93328399999999</v>
       </c>
     </row>
     <row r="49" spans="2:2">
       <c r="B49">
-        <f>POWER(B19,2)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50">
-        <f>POWER(B20,2)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="2:2">
       <c r="B51">
-        <f>POWER(B21,2)</f>
+        <f t="shared" si="4"/>
         <v>144</v>
       </c>
     </row>
     <row r="52" spans="2:2">
       <c r="B52">
-        <f>B36+B44</f>
+        <f t="shared" ref="B52:B59" si="5">B36+B44</f>
         <v>540160.37679399992</v>
       </c>
     </row>
     <row r="53" spans="2:2">
       <c r="B53">
-        <f>B37+B45</f>
+        <f t="shared" si="5"/>
         <v>1519539.23092</v>
       </c>
     </row>
     <row r="54" spans="2:2">
       <c r="B54">
-        <f>B38+B46</f>
+        <f t="shared" si="5"/>
         <v>2561692.6142180003</v>
       </c>
     </row>
     <row r="55" spans="2:2">
       <c r="B55">
-        <f>B39+B47</f>
+        <f t="shared" si="5"/>
         <v>1241851.8717090001</v>
       </c>
     </row>
     <row r="56" spans="2:2">
       <c r="B56">
-        <f>B40+B48</f>
+        <f t="shared" si="5"/>
         <v>146.10236499999999</v>
       </c>
     </row>
     <row r="57" spans="2:2">
       <c r="B57">
-        <f>B41+B49</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="2:2">
       <c r="B58">
-        <f>B42+B50</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="2:2">
       <c r="B59">
-        <f>B43+B51</f>
+        <f t="shared" si="5"/>
         <v>144</v>
       </c>
     </row>
     <row r="60" spans="2:2">
       <c r="B60">
-        <f>A14*B52</f>
+        <f t="shared" ref="B60:B67" si="6">A14*B52</f>
         <v>92907584.808567986</v>
       </c>
     </row>
     <row r="61" spans="2:2">
       <c r="B61">
-        <f>A15*B53</f>
+        <f t="shared" si="6"/>
         <v>629089241.60088003</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62">
-        <f>A16*B54</f>
+        <f t="shared" si="6"/>
         <v>540517141.59999812</v>
       </c>
     </row>
     <row r="63" spans="2:2">
       <c r="B63">
-        <f>A17*B55</f>
+        <f t="shared" si="6"/>
         <v>239677411.23983702</v>
       </c>
     </row>
     <row r="64" spans="2:2">
       <c r="B64">
-        <f>A18*B56</f>
+        <f t="shared" si="6"/>
         <v>1314.9212849999999</v>
       </c>
     </row>
     <row r="65" spans="2:2">
       <c r="B65">
-        <f>A19*B57</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="2:2">
       <c r="B66">
-        <f>A20*B58</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="2:2">
       <c r="B67">
-        <f>A21*B59</f>
+        <f t="shared" si="6"/>
         <v>144</v>
       </c>
     </row>
